--- a/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
+++ b/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\My Drive\Tài liệu kỹ thuật thiết bị\VNSH03\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\VNSH03\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1617E82D-DE6E-43D9-A217-CCCDA2078716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -635,7 +636,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -700,9 +701,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -719,26 +719,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1019,750 +1016,748 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="6" width="44.140625" customWidth="1"/>
     <col min="7" max="7" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="11"/>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="4" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="4"/>
+      <c r="F5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+      <c r="G5" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-      <c r="B7" s="4" t="s">
+      <c r="G6" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
-      <c r="B8" s="4" t="s">
+      <c r="G7" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="11"/>
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="4" t="s">
+      <c r="G8" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="220.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="4" t="s">
+      <c r="G9" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="220.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="4" t="s">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="4"/>
+      <c r="F11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="4" t="s">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="4" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="G12" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="63" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
         <v>40</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+    <row r="14" spans="1:7" ht="204.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>41</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="252" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="G14" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="252" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="G15" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
         <v>44</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="2">
         <v>51</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="2">
         <v>60</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="2">
         <v>61</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="2">
         <v>66</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="11">
         <v>4</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="5" t="s">
+      <c r="A22" s="11"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="4" t="s">
+      <c r="E22" s="9"/>
+      <c r="F22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="2">
         <v>91</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="5"/>
-      <c r="E23" s="4" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="2">
         <v>39</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="2">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="4"/>
+      <c r="F25" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="5"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="2">
         <v>6</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="4" t="s">
+      <c r="E26" s="4"/>
+      <c r="F26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="2">
         <v>65</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="5"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="4" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="2">
         <v>29</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="4" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="2">
         <v>3</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="4" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="5"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="A31" s="2">
         <v>5</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="4" t="s">
+      <c r="E31" s="4"/>
+      <c r="F31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="A32" s="2">
         <v>49</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="4"/>
+      <c r="F32" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A33" s="5"/>
-      <c r="B33" s="5" t="s">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5" t="s">
+      <c r="E33" s="4"/>
+      <c r="F33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11" t="s">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="11"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="11"/>
-      <c r="B35" s="13" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="11" t="s">
+      <c r="E35" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="11"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="11"/>
-      <c r="B36" s="13" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G36" s="11"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="11"/>
-      <c r="B37" s="13" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="11"/>
+      <c r="G37" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
+++ b/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\VNSH03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1617E82D-DE6E-43D9-A217-CCCDA2078716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B607AA9-9239-4457-B1BF-B28B2B3B14A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="147">
   <si>
     <t>BẢNG LỆNH CẤU HÌNH THIẾT BỊ VNSH03</t>
   </si>
@@ -632,12 +632,39 @@
     <t>Camera 1 mirror disabled =&gt; đóng
 Camera 1 mirror enabled =&gt; mở</t>
   </si>
+  <si>
+    <t>c:trks:ota:http://white.aithings.vn:13579/RK3562/FW/tracker_service;</t>
+  </si>
+  <si>
+    <t>c:cons:ota:http://white.aithings.vn:13579/RK3562/FW/control_service;</t>
+  </si>
+  <si>
+    <t>c:cams:ota:http://white.aithings.vn:13579/RK3562/FW/camera_service;</t>
+  </si>
+  <si>
+    <t>c:cons:ftpcfg:ftp://ftp-vnsh03.vnetgps.net;logftp;@AaQqQ;</t>
+  </si>
+  <si>
+    <t>HTKT báo cấu hình</t>
+  </si>
+  <si>
+    <t>Cấu hình server ảnh</t>
+  </si>
+  <si>
+    <t>Xử lý dữ liệu cảm biến</t>
+  </si>
+  <si>
+    <t>Xử lý lỗi sụt áp</t>
+  </si>
+  <si>
+    <t>Cấu hình cam</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,6 +683,18 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF081B3A"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -701,41 +740,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1017,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="6" width="44.140625" customWidth="1"/>
@@ -1025,15 +1069,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1054,710 +1098,770 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
+      <c r="A3" s="8">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="11"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="4"/>
+      <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="11"/>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="220.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="3" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="4"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="3" t="s">
+      <c r="E11" s="7"/>
+      <c r="F11" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="4"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3" t="s">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>40</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <v>41</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <v>42</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
+      <c r="A16" s="10">
         <v>44</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
+      <c r="A17" s="10">
         <v>51</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2">
+      <c r="A18" s="10">
         <v>60</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="2">
+      <c r="A19" s="10">
         <v>61</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="10">
         <v>66</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="11">
+      <c r="A21" s="8">
         <v>4</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="4" t="s">
+      <c r="A22" s="8"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="11"/>
+      <c r="F22" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
+      <c r="A23" s="10">
         <v>91</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="3" t="s">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
+      <c r="A24" s="10">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="7" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
+      <c r="A25" s="10">
         <v>2</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="4"/>
-      <c r="F25" s="3" t="s">
+      <c r="E25" s="7"/>
+      <c r="F25" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="4"/>
+      <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
+      <c r="A26" s="10">
         <v>6</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="4"/>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="7"/>
+      <c r="F26" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="7" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
+      <c r="A27" s="10">
         <v>65</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
+      <c r="A28" s="10">
         <v>27</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="7"/>
+      <c r="F28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
+      <c r="A29" s="10">
         <v>29</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="3" t="s">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
+      <c r="A30" s="10">
         <v>3</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="D30" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="7"/>
+      <c r="F30" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="4"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
+      <c r="A31" s="10">
         <v>5</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="3" t="s">
+      <c r="E31" s="7"/>
+      <c r="F31" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
+      <c r="A32" s="10">
         <v>49</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="4"/>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="7"/>
+      <c r="F32" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4" t="s">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4" t="s">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8" t="s">
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="8"/>
+      <c r="G34" s="9"/>
     </row>
     <row r="35" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="4" t="s">
+      <c r="A35" s="9"/>
+      <c r="B35" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="8"/>
+      <c r="G35" s="9"/>
     </row>
     <row r="36" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="9"/>
+      <c r="B36" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="E36" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G36" s="8"/>
+      <c r="G36" s="9"/>
     </row>
     <row r="37" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="4" t="s">
+      <c r="A37" s="9"/>
+      <c r="B37" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="8"/>
+      <c r="G37" s="9"/>
+    </row>
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="6"/>
+      <c r="D39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="6"/>
+      <c r="D40" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="6"/>
+      <c r="D41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
+++ b/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\VNSH03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B607AA9-9239-4457-B1BF-B28B2B3B14A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4061FF25-944E-44B2-AE85-8482D77594FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -748,9 +748,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -769,17 +766,20 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1069,15 +1069,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -1103,763 +1103,763 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="13">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="13"/>
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="7"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="13"/>
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="6"/>
+      <c r="F5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="13">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7" t="s">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="299.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="157.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7" t="s">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="220.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="7"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="13"/>
+      <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7" t="s">
+      <c r="E11" s="6"/>
+      <c r="F11" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="7"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7" t="s">
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="7">
         <v>40</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="204.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="7">
         <v>41</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="7">
         <v>42</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="7">
         <v>44</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="7">
         <v>51</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="7">
         <v>60</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="7">
         <v>61</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="7">
         <v>66</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="13">
         <v>4</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>77</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
+      <c r="A22" s="13"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>79</v>
       </c>
       <c r="E22" s="11"/>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="110.25" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="7">
         <v>91</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="7">
         <v>39</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="7">
         <v>2</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7" t="s">
+      <c r="E25" s="6"/>
+      <c r="F25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="7"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="7">
         <v>6</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7" t="s">
+      <c r="E26" s="6"/>
+      <c r="F26" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="6" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="7">
         <v>65</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="7"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7" t="s">
+      <c r="E28" s="6"/>
+      <c r="F28" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="7">
         <v>29</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7" t="s">
+      <c r="E29" s="6"/>
+      <c r="F29" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="7">
         <v>3</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7" t="s">
+      <c r="E30" s="6"/>
+      <c r="F30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="7"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" spans="1:7" ht="63" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="7">
         <v>5</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="6"/>
+      <c r="F31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="141.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="7">
         <v>49</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7" t="s">
+      <c r="E32" s="6"/>
+      <c r="F32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="126" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7" t="s">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="6"/>
+      <c r="F33" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="252" x14ac:dyDescent="0.25">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9" t="s">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9" t="s">
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G34" s="9"/>
+      <c r="G34" s="8"/>
     </row>
     <row r="35" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A35" s="9"/>
-      <c r="B35" s="7" t="s">
+      <c r="A35" s="8"/>
+      <c r="B35" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="G35" s="9"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A36" s="9"/>
-      <c r="B36" s="7" t="s">
+      <c r="A36" s="8"/>
+      <c r="B36" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="G36" s="9"/>
+      <c r="G36" s="8"/>
     </row>
     <row r="37" spans="1:7" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="9"/>
-      <c r="B37" s="7" t="s">
+      <c r="A37" s="8"/>
+      <c r="B37" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="9"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="13" t="s">
+      <c r="A38" s="4"/>
+      <c r="B38" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="4" t="s">
+      <c r="C38" s="5"/>
+      <c r="D38" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="6" t="s">
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="13" t="s">
+      <c r="A39" s="4"/>
+      <c r="B39" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="4" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="6" t="s">
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="6" t="s">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="4" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="6" t="s">
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="13" t="s">
+      <c r="A41" s="4"/>
+      <c r="B41" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="4" t="s">
+      <c r="C41" s="5"/>
+      <c r="D41" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="6" t="s">
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="5" t="s">
         <v>142</v>
       </c>
     </row>

--- a/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
+++ b/3. G_Documents/4. Tài liệu/VNSH03/Bảng lệnh cầu hình VNSH03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\3. G_Documents\4. Tài liệu\VNSH03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4061FF25-944E-44B2-AE85-8482D77594FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279722D1-44C1-40D4-9F0B-9584A1F9CA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
